--- a/Orçado/Orça-Seringal/VERA CRUZ - SERINGAL.xlsx
+++ b/Orçado/Orça-Seringal/VERA CRUZ - SERINGAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Seringal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598971DB-860A-444C-B9B7-BE6FF11D3219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D6EDE-D0D2-44D4-BF5E-B86E0EC7D27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{1C8DD9CB-E6BE-4A6E-8C2B-E798776C77D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8DD9CB-E6BE-4A6E-8C2B-E798776C77D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="93">
   <si>
     <t>4.1.01.01.0001</t>
   </si>
@@ -231,6 +231,93 @@
   </si>
   <si>
     <t>RATEIO RECEBIDO</t>
+  </si>
+  <si>
+    <t>RATEIO CARRETAS AGRICOLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS TANQUE </t>
+  </si>
+  <si>
+    <t>RATEIO CONFRATERNIZACOES E EVENTOS COM COLABORADORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO MEDICINA E SEGURANCA DO TRABALHO </t>
+  </si>
+  <si>
+    <t>RATEIO MOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO OFICINA </t>
+  </si>
+  <si>
+    <t>RATEIO PROGRAMA INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>RATEIO PROJETOS DESENVOLVIMENTO HUMANO</t>
+  </si>
+  <si>
+    <t>RATEIO PULVERIZADORES</t>
+  </si>
+  <si>
+    <t>RATEIO SUPERVISAO SERINGUEIRA</t>
+  </si>
+  <si>
+    <t>RATEIO TRATORES LEVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO TRATORES MEDIOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS LEVES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS MEDIOS </t>
+  </si>
+  <si>
+    <t>4.2.01.02.0034</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0045</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0017</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0018</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0024</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0064</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0047</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0035</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0020</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0066</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0051</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0037</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0021</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0036</t>
+  </si>
+  <si>
+    <t>FRETES E CARRETOS PJ</t>
   </si>
 </sst>
 </file>
@@ -667,12 +754,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4980F707-C98A-4869-ACDC-AF55442E10D3}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="4"/>
   </cols>
@@ -849,7 +936,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D5" s="4">
         <v>409.43</v>
@@ -1733,46 +1820,395 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="4">
+        <v>6.52</v>
+      </c>
+      <c r="E27" s="4">
+        <v>6.8133999999999988</v>
+      </c>
+      <c r="F27" s="4">
+        <v>6.8133999999999988</v>
+      </c>
+      <c r="G27" s="4">
+        <v>6.8133999999999988</v>
+      </c>
+      <c r="H27" s="4">
+        <v>6.8133999999999988</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>7.3149999999999995</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1.9541500000000001</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="H28" s="4">
+        <v>11.202399999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1285.3999999999999</v>
+      </c>
+      <c r="E29" s="4">
+        <v>825.1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>88</v>
+      </c>
+      <c r="G29" s="4">
+        <v>88</v>
+      </c>
+      <c r="H29" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="4">
+        <v>235</v>
+      </c>
+      <c r="E30" s="4">
+        <v>235</v>
+      </c>
+      <c r="F30" s="4">
+        <v>245.57499999999999</v>
+      </c>
+      <c r="G30" s="4">
+        <v>245.57499999999999</v>
+      </c>
+      <c r="H30" s="4">
+        <v>245.57499999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="4">
+        <v>11.12</v>
+      </c>
+      <c r="E33" s="4">
+        <v>11.620399999999998</v>
+      </c>
+      <c r="F33" s="4">
+        <v>11.620399999999998</v>
+      </c>
+      <c r="G33" s="4">
+        <v>11.620399999999998</v>
+      </c>
+      <c r="H33" s="4">
+        <v>11.620399999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="4">
+        <v>28.54</v>
+      </c>
+      <c r="E34" s="4">
+        <v>29.824299999999997</v>
+      </c>
+      <c r="F34" s="4">
+        <v>29.824299999999997</v>
+      </c>
+      <c r="G34" s="4">
+        <v>29.824299999999997</v>
+      </c>
+      <c r="H34" s="4">
+        <v>29.824299999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="4">
+        <v>44</v>
+      </c>
+      <c r="E35" s="4">
+        <v>20.9</v>
+      </c>
+      <c r="F35" s="4">
+        <v>31.349999999999998</v>
+      </c>
+      <c r="G35" s="4">
+        <v>17.765000000000001</v>
+      </c>
+      <c r="H35" s="4">
+        <v>31.349999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" t="s">
         <v>25</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C36" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="4">
-        <v>2862.7474632580552</v>
-      </c>
-      <c r="E27" s="4">
-        <v>3020.2801931166555</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1745.631324123972</v>
-      </c>
-      <c r="G27" s="4">
-        <v>3925.5525161239716</v>
-      </c>
-      <c r="H27" s="4">
-        <v>2350.4805461239721</v>
-      </c>
-      <c r="I27" s="4">
+      <c r="I36" s="4">
         <v>2500.7165838614974</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J36" s="4">
         <v>3936.8243138614971</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K36" s="4">
         <v>5284.620749708015</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L36" s="4">
         <v>2915.6892581715174</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M36" s="4">
         <v>1913.2890518260165</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N36" s="4">
         <v>1822.3318619615047</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O36" s="4">
         <v>1944.2385195159804</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1156.1674632580555</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1208.6370931166555</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1230.1740741239721</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1768.7869161239719</v>
+      </c>
+      <c r="H37" s="4">
+        <v>1260.4300461239723</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <v>574.75</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1654.2349999999999</v>
+      </c>
+      <c r="H38" s="4">
+        <v>565.34499999999991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="4">
+        <v>96</v>
+      </c>
+      <c r="E40" s="4">
+        <v>100.32</v>
+      </c>
+      <c r="F40" s="4">
+        <v>100.32</v>
+      </c>
+      <c r="G40" s="4">
+        <v>100.32</v>
+      </c>
+      <c r="H40" s="4">
+        <v>100.32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
